--- a/inst/extdata/translations.xlsx
+++ b/inst/extdata/translations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
     <t xml:space="preserve">english</t>
   </si>
@@ -1362,6 +1362,174 @@
   </si>
   <si>
     <t xml:space="preserve">Informations système</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Custom Mitigations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Télécharger le rapport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom Mitigations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Mitigations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove Created Mitigations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No mitigation measures apply to these activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">validations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are duplicate short names in Mitigations. These should be unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on an edge to create a mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear your selection (click on the background) and try clicking on an edge (not an activity) to create a mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problems with the mitigations file, contact the CWS team and report the following</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activities must be selected before mitigation measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currently selected edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already have custom mitigation for this edge. Delete or choose another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table of Contents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mines and Metal Mills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear Facilities, including certain storage and Long-term Management or Disposal facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onshore Oil, Gas and other Fossil Fuels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical Transmission Lines and Pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renewable Energy – Hydroelectric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazardous Waste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marine Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aerodrome (including runways)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Military bases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canal or lock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquaculture facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renewable Energy – Land based Wind Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR15</t>
   </si>
 </sst>
 </file>
@@ -4015,6 +4183,391 @@
         <v>421</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>450</v>
+      </c>
+      <c r="B247" t="s">
+        <v>386</v>
+      </c>
+      <c r="C247" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>421</v>
+      </c>
+      <c r="B248" t="s">
+        <v>452</v>
+      </c>
+      <c r="C248" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>453</v>
+      </c>
+      <c r="B249" t="s">
+        <v>454</v>
+      </c>
+      <c r="C249" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>455</v>
+      </c>
+      <c r="B250" t="s">
+        <v>386</v>
+      </c>
+      <c r="C250" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>456</v>
+      </c>
+      <c r="B251" t="s">
+        <v>386</v>
+      </c>
+      <c r="C251" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>457</v>
+      </c>
+      <c r="B252" t="s">
+        <v>386</v>
+      </c>
+      <c r="C252" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>458</v>
+      </c>
+      <c r="B253" t="s">
+        <v>386</v>
+      </c>
+      <c r="C253" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>460</v>
+      </c>
+      <c r="B254" t="s">
+        <v>386</v>
+      </c>
+      <c r="C254" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>462</v>
+      </c>
+      <c r="B255" t="s">
+        <v>386</v>
+      </c>
+      <c r="C255" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>463</v>
+      </c>
+      <c r="B256" t="s">
+        <v>386</v>
+      </c>
+      <c r="C256" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>464</v>
+      </c>
+      <c r="B257" t="s">
+        <v>386</v>
+      </c>
+      <c r="C257" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>465</v>
+      </c>
+      <c r="B258" t="s">
+        <v>386</v>
+      </c>
+      <c r="C258" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>466</v>
+      </c>
+      <c r="B259" t="s">
+        <v>386</v>
+      </c>
+      <c r="C259" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>467</v>
+      </c>
+      <c r="B260" t="s">
+        <v>386</v>
+      </c>
+      <c r="C260" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>469</v>
+      </c>
+      <c r="B261" t="s">
+        <v>386</v>
+      </c>
+      <c r="C261" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>470</v>
+      </c>
+      <c r="B262" t="s">
+        <v>386</v>
+      </c>
+      <c r="C262" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>471</v>
+      </c>
+      <c r="B263" t="s">
+        <v>386</v>
+      </c>
+      <c r="C263" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>472</v>
+      </c>
+      <c r="B264" t="s">
+        <v>386</v>
+      </c>
+      <c r="C264" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>473</v>
+      </c>
+      <c r="B265" t="s">
+        <v>386</v>
+      </c>
+      <c r="C265" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>474</v>
+      </c>
+      <c r="B266" t="s">
+        <v>386</v>
+      </c>
+      <c r="C266" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>475</v>
+      </c>
+      <c r="B267" t="s">
+        <v>476</v>
+      </c>
+      <c r="C267" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>478</v>
+      </c>
+      <c r="B268" t="s">
+        <v>479</v>
+      </c>
+      <c r="C268" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>480</v>
+      </c>
+      <c r="B269" t="s">
+        <v>481</v>
+      </c>
+      <c r="C269" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>482</v>
+      </c>
+      <c r="B270" t="s">
+        <v>483</v>
+      </c>
+      <c r="C270" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>484</v>
+      </c>
+      <c r="B271" t="s">
+        <v>485</v>
+      </c>
+      <c r="C271" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>486</v>
+      </c>
+      <c r="B272" t="s">
+        <v>487</v>
+      </c>
+      <c r="C272" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>488</v>
+      </c>
+      <c r="B273" t="s">
+        <v>489</v>
+      </c>
+      <c r="C273" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>490</v>
+      </c>
+      <c r="B274" t="s">
+        <v>491</v>
+      </c>
+      <c r="C274" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>492</v>
+      </c>
+      <c r="B275" t="s">
+        <v>493</v>
+      </c>
+      <c r="C275" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>494</v>
+      </c>
+      <c r="B276" t="s">
+        <v>495</v>
+      </c>
+      <c r="C276" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>496</v>
+      </c>
+      <c r="B277" t="s">
+        <v>497</v>
+      </c>
+      <c r="C277" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>498</v>
+      </c>
+      <c r="B278" t="s">
+        <v>499</v>
+      </c>
+      <c r="C278" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>500</v>
+      </c>
+      <c r="B279" t="s">
+        <v>501</v>
+      </c>
+      <c r="C279" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>502</v>
+      </c>
+      <c r="B280" t="s">
+        <v>503</v>
+      </c>
+      <c r="C280" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>504</v>
+      </c>
+      <c r="B281" t="s">
+        <v>505</v>
+      </c>
+      <c r="C281" t="s">
+        <v>477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
